--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.58664</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.10336</v>
+      </c>
+      <c r="E4" t="n">
         <v>16.51815</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16.58664</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.10336</v>
       </c>
       <c r="F4" t="n">
         <v>41.75921</v>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.37829</v>
+        <v>16.38595</v>
       </c>
       <c r="D8" t="n">
         <v>15.91238</v>
       </c>
       <c r="E8" t="n">
-        <v>16.38595</v>
+        <v>16.37829</v>
       </c>
       <c r="F8" t="n">
         <v>21.72054</v>
